--- a/data/trans_orig/Q5402-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q5402-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si son capaces de prepararse la comida en 2007</t>
+          <t>Población según si son capaces de prepararse la comida en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16292</t>
+          <t>15636</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34317</t>
+          <t>33436</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22673</t>
+          <t>23801</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46882</t>
+          <t>47719</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>45198</t>
+          <t>43644</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>74878</t>
+          <t>74235</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,73%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26332</t>
+          <t>26422</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46520</t>
+          <t>47273</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>32732</t>
+          <t>31583</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>58052</t>
+          <t>57927</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>62019</t>
+          <t>62873</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>97165</t>
+          <t>95426</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>9,93%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>299013</t>
+          <t>299140</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>326396</t>
+          <t>326107</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>80,12%</t>
+          <t>80,16%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>492900</t>
+          <t>492507</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>525712</t>
+          <t>526477</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>800975</t>
+          <t>802208</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>844924</t>
+          <t>843067</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>83,35%</t>
+          <t>83,48%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>87,73%</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4812</t>
+          <t>3983</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>913</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8565</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>1032</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>10396</t>
+          <t>10970</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,3%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4239</t>
+          <t>3569</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15014</t>
+          <t>13649</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1099</t>
+          <t>1086</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9175</t>
+          <t>8922</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>5857</t>
+          <t>6414</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>19462</t>
+          <t>19084</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,7%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>71760</t>
+          <t>72687</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>83059</t>
+          <t>83611</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>81,47%</t>
+          <t>82,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>49539</t>
+          <t>48444</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>59918</t>
+          <t>59842</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>77,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>125751</t>
+          <t>126606</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>141323</t>
+          <t>141361</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>84,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,06%</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5083</t>
+          <t>4390</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,62 +1680,62 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>955</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>1829</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>3993</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>6,81%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>955</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>4933</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>5,87%</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10792</t>
+          <t>10997</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6621</t>
+          <t>6361</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1652</t>
+          <t>1658</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13065</t>
+          <t>12824</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>18,84%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>29504</t>
+          <t>29951</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>40204</t>
+          <t>40235</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,62%</t>
+          <t>72,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>20260</t>
+          <t>20520</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,37%</t>
+          <t>76,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>53522</t>
+          <t>54116</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>65756</t>
+          <t>65990</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,62%</t>
+          <t>79,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,94%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18020</t>
+          <t>18047</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>37982</t>
+          <t>36846</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>26394</t>
+          <t>25721</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>51806</t>
+          <t>50848</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>49261</t>
+          <t>49142</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>80333</t>
+          <t>79749</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,76%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>35508</t>
+          <t>36290</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>61047</t>
+          <t>62253</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>35913</t>
+          <t>36409</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>62298</t>
+          <t>63520</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>78899</t>
+          <t>78855</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>117050</t>
+          <t>115365</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,78%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>412231</t>
+          <t>412889</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>443373</t>
+          <t>443230</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>82,17%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>572581</t>
+          <t>571453</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>608600</t>
+          <t>607620</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>84,43%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>998075</t>
+          <t>994367</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1043331</t>
+          <t>1041130</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>88,28%</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2593,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si son capaces de prepararse la comida en 2012</t>
+          <t>Población según si son capaces de prepararse la comida en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>37573</t>
+          <t>36802</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>65544</t>
+          <t>65622</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>55585</t>
+          <t>54736</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>89429</t>
+          <t>87043</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>100108</t>
+          <t>100038</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>144367</t>
+          <t>143386</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,67%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>38150</t>
+          <t>38766</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>66530</t>
+          <t>69957</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>51813</t>
+          <t>53158</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>82559</t>
+          <t>85027</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>98513</t>
+          <t>98460</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>142174</t>
+          <t>141487</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,49%</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>293421</t>
+          <t>289640</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>329656</t>
+          <t>329361</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>69,89%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>79,55%</t>
+          <t>79,48%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>473666</t>
+          <t>474261</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>516494</t>
+          <t>517068</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>74,65%</t>
+          <t>74,74%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>81,49%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>777322</t>
+          <t>778679</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>835787</t>
+          <t>833587</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>74,23%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>79,68%</t>
+          <t>79,47%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1019</t>
+          <t>1009</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9495</t>
+          <t>9927</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8340</t>
+          <t>8026</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2325</t>
+          <t>2354</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>14444</t>
+          <t>12960</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>6,42%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6479</t>
+          <t>6201</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21309</t>
+          <t>21566</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2052</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10952</t>
+          <t>11681</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>10364</t>
+          <t>10439</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>27430</t>
+          <t>27438</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>92944</t>
+          <t>91963</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>109492</t>
+          <t>109632</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>77,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>68765</t>
+          <t>68564</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>79812</t>
+          <t>79895</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>166875</t>
+          <t>167486</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>186315</t>
+          <t>186325</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>83,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,36%</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3705,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>4692</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5031</t>
+          <t>5753</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3775,7 +3775,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6100</t>
+          <t>6606</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>13,53%</t>
         </is>
       </c>
     </row>
@@ -3818,7 +3818,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5362</t>
+          <t>5089</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3833,7 +3833,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6585</t>
+          <t>7114</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3868,7 +3868,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>984</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9201</t>
+          <t>8780</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>17,98%</t>
         </is>
       </c>
     </row>
@@ -3926,7 +3926,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>19744</t>
+          <t>19534</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>73,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13928</t>
+          <t>13781</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21262</t>
+          <t>21242</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,61%</t>
+          <t>61,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>37338</t>
+          <t>37117</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>46786</t>
+          <t>46756</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>76,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,77%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>40741</t>
+          <t>41497</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>70311</t>
+          <t>70429</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>59141</t>
+          <t>58957</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>92210</t>
+          <t>91726</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>109516</t>
+          <t>105848</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>152784</t>
+          <t>153107</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,78%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>49285</t>
+          <t>51034</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>83806</t>
+          <t>82120</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>58540</t>
+          <t>59142</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>91367</t>
+          <t>91274</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>119455</t>
+          <t>117676</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>163736</t>
+          <t>164039</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,62%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>416624</t>
+          <t>417477</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>458060</t>
+          <t>459168</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>74,45%</t>
+          <t>74,6%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>82,05%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>567130</t>
+          <t>569514</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>611303</t>
+          <t>611605</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>76,65%</t>
+          <t>76,98%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1001554</t>
+          <t>999509</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1061686</t>
+          <t>1059529</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>76,91%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>81,53%</t>
         </is>
       </c>
     </row>
@@ -4648,7 +4648,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si son capaces de prepararse la comida en 2016</t>
+          <t>Población según si son capaces de prepararse la comida en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4843,12 +4843,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20351</t>
+          <t>19749</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38652</t>
+          <t>37868</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30928</t>
+          <t>31498</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>59194</t>
+          <t>60877</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>57092</t>
+          <t>56553</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>91749</t>
+          <t>90863</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,0%</t>
         </is>
       </c>
     </row>
@@ -4956,12 +4956,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29134</t>
+          <t>28190</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>50967</t>
+          <t>50764</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39089</t>
+          <t>40246</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>70531</t>
+          <t>70599</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>74207</t>
+          <t>74491</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>111519</t>
+          <t>112545</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,39%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>273070</t>
+          <t>271975</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>299887</t>
+          <t>300921</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>76,85%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>435516</t>
+          <t>437572</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>477199</t>
+          <t>475627</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>78,88%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>85,74%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>719100</t>
+          <t>720267</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>766772</t>
+          <t>768355</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>79,27%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>84,56%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1992</t>
+          <t>2064</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12285</t>
+          <t>12644</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1318</t>
+          <t>1340</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>15534</t>
+          <t>15544</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5349,7 +5349,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5735</t>
+          <t>5164</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>21788</t>
+          <t>21537</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,66%</t>
         </is>
       </c>
     </row>
@@ -5412,12 +5412,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3983</t>
+          <t>4032</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14103</t>
+          <t>14671</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5427,12 +5427,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7052</t>
+          <t>7554</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>24879</t>
+          <t>25882</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>14439</t>
+          <t>14587</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>34875</t>
+          <t>34545</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,08%</t>
         </is>
       </c>
     </row>
@@ -5525,12 +5525,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>170918</t>
+          <t>169704</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>184546</t>
+          <t>184195</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>155636</t>
+          <t>156269</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>176919</t>
+          <t>176723</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>82,75%</t>
+          <t>83,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>331007</t>
+          <t>333291</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>356922</t>
+          <t>357033</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,81%</t>
         </is>
       </c>
     </row>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3690</t>
+          <t>4358</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5790,62 +5790,62 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>868</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>2376</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>4428</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>7,06%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>868</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>5849</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>5,85%</t>
         </is>
       </c>
     </row>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5152</t>
+          <t>5542</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5908,7 +5908,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12439</t>
+          <t>11657</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5923,7 +5923,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1481</t>
+          <t>1395</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14414</t>
+          <t>12494</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>16,5%</t>
         </is>
       </c>
     </row>
@@ -5981,12 +5981,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>35768</t>
+          <t>34522</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>41340</t>
+          <t>41306</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5996,12 +5996,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>82,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>21235</t>
+          <t>22017</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>65,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>59571</t>
+          <t>61799</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>73447</t>
+          <t>73913</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6066,12 +6066,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>81,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,64%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25868</t>
+          <t>26176</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>46708</t>
+          <t>47445</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>35487</t>
+          <t>35967</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>66657</t>
+          <t>67114</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>66713</t>
+          <t>68487</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>104200</t>
+          <t>105172</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,71%</t>
         </is>
       </c>
     </row>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>36326</t>
+          <t>36147</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>60860</t>
+          <t>60935</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6339,12 +6339,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>54343</t>
+          <t>53733</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>92477</t>
+          <t>89692</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6374,12 +6374,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>94862</t>
+          <t>97526</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>141861</t>
+          <t>142808</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,46%</t>
         </is>
       </c>
     </row>
@@ -6437,12 +6437,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>489790</t>
+          <t>490286</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>519536</t>
+          <t>520941</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>631284</t>
+          <t>630354</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>677244</t>
+          <t>678442</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6487,12 +6487,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>81,3%</t>
+          <t>81,18%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1134585</t>
+          <t>1131310</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1189218</t>
+          <t>1187402</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>86,99%</t>
         </is>
       </c>
     </row>
@@ -6703,7 +6703,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si son capaces de prepararse la comida en 2023</t>
+          <t>Población según si son capaces de prepararse la comida en 2023 (tasa de respuesta: 99,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6898,12 +6898,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26443</t>
+          <t>26730</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43288</t>
+          <t>43447</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6913,12 +6913,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>58695</t>
+          <t>57884</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>81971</t>
+          <t>81776</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6968,12 +6968,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>90382</t>
+          <t>88851</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>116811</t>
+          <t>117511</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,3%</t>
         </is>
       </c>
     </row>
@@ -7011,12 +7011,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29610</t>
+          <t>29560</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>48667</t>
+          <t>46841</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7026,12 +7026,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>62686</t>
+          <t>63729</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>84549</t>
+          <t>86050</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7061,12 +7061,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>97570</t>
+          <t>99665</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>126441</t>
+          <t>127225</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7096,12 +7096,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,57%</t>
         </is>
       </c>
     </row>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>183840</t>
+          <t>182125</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>206713</t>
+          <t>204529</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>68,84%</t>
+          <t>68,19%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>342818</t>
+          <t>342309</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>370540</t>
+          <t>371135</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>68,36%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>74,0%</t>
+          <t>74,12%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>534333</t>
+          <t>533636</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>570915</t>
+          <t>569796</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7209,12 +7209,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>69,5%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>74,36%</t>
+          <t>74,21%</t>
         </is>
       </c>
     </row>
@@ -7354,12 +7354,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7638</t>
+          <t>7714</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18864</t>
+          <t>18503</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7369,12 +7369,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1384</t>
+          <t>1405</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13443</t>
+          <t>13223</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7404,12 +7404,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>7823</t>
+          <t>7619</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>28889</t>
+          <t>29086</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7439,12 +7439,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -7467,12 +7467,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13170</t>
+          <t>12961</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26621</t>
+          <t>26951</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7482,12 +7482,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7415</t>
+          <t>8042</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>47250</t>
+          <t>46339</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7517,12 +7517,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>18706</t>
+          <t>16721</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>64290</t>
+          <t>62748</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7552,12 +7552,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,61%</t>
         </is>
       </c>
     </row>
@@ -7580,12 +7580,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>232750</t>
+          <t>232510</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>249466</t>
+          <t>249622</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>397509</t>
+          <t>398924</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>446304</t>
+          <t>445571</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>638392</t>
+          <t>639950</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>703223</t>
+          <t>702965</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,43%</t>
         </is>
       </c>
     </row>
@@ -7810,12 +7810,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>160</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5392</t>
+          <t>5172</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7830,7 +7830,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7860,12 +7860,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>158</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5387</t>
+          <t>4574</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7900,7 +7900,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -7923,12 +7923,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3391</t>
+          <t>3383</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11290</t>
+          <t>11257</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2197</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8587</t>
+          <t>8801</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7973,12 +7973,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7993,12 +7993,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7114</t>
+          <t>7044</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17332</t>
+          <t>16539</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8008,12 +8008,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,38%</t>
         </is>
       </c>
     </row>
@@ -8036,12 +8036,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>91760</t>
+          <t>91710</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>100322</t>
+          <t>100356</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8071,12 +8071,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>62738</t>
+          <t>62524</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>69128</t>
+          <t>69008</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8106,12 +8106,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>157021</t>
+          <t>158247</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>167850</t>
+          <t>168117</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,35%</t>
         </is>
       </c>
     </row>
@@ -8266,12 +8266,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>38156</t>
+          <t>39291</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>58574</t>
+          <t>59500</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8281,12 +8281,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>38720</t>
+          <t>36775</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>99080</t>
+          <t>97884</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8316,12 +8316,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>83096</t>
+          <t>82839</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>146969</t>
+          <t>149750</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,95%</t>
         </is>
       </c>
     </row>
@@ -8379,12 +8379,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>52266</t>
+          <t>52336</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>76051</t>
+          <t>77099</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8394,12 +8394,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>51777</t>
+          <t>47962</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>132617</t>
+          <t>132443</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8429,12 +8429,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>106671</t>
+          <t>97880</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>196186</t>
+          <t>195466</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8464,12 +8464,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,68%</t>
         </is>
       </c>
     </row>
@@ -8492,12 +8492,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>518386</t>
+          <t>518255</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>547946</t>
+          <t>547974</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8507,12 +8507,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>80,31%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8527,12 +8527,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>799104</t>
+          <t>799879</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>932859</t>
+          <t>943821</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8542,12 +8542,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>77,75%</t>
+          <t>77,82%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8562,12 +8562,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1336096</t>
+          <t>1334668</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1483478</t>
+          <t>1484238</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8577,12 +8577,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,71%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q5402-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q5402-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15636</t>
+          <t>15867</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33436</t>
+          <t>34375</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23801</t>
+          <t>22429</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47719</t>
+          <t>47192</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>43644</t>
+          <t>45541</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>74235</t>
+          <t>75667</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,87%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26422</t>
+          <t>26148</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>47273</t>
+          <t>46725</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>31583</t>
+          <t>32634</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>57927</t>
+          <t>58868</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>62873</t>
+          <t>64664</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>95426</t>
+          <t>97033</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,1%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>299140</t>
+          <t>299321</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>326107</t>
+          <t>325685</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>80,16%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>87,27%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>492507</t>
+          <t>489831</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>526477</t>
+          <t>525143</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>83,34%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>802208</t>
+          <t>801049</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>843067</t>
+          <t>844206</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>87,85%</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3983</t>
+          <t>4660</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>913</t>
+          <t>904</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>8599</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1032</t>
+          <t>1127</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>10970</t>
+          <t>10064</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>6,7%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3569</t>
+          <t>4248</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13649</t>
+          <t>14047</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1086</t>
+          <t>1097</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8922</t>
+          <t>8970</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>6414</t>
+          <t>6060</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>19084</t>
+          <t>18548</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,34%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>72687</t>
+          <t>72978</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>83611</t>
+          <t>83471</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>82,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>48444</t>
+          <t>48942</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>59842</t>
+          <t>59882</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>77,87%</t>
+          <t>78,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>126606</t>
+          <t>126400</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>141361</t>
+          <t>140913</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>93,76%</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4390</t>
+          <t>5226</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3993</t>
+          <t>4940</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>7,26%</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10997</t>
+          <t>9722</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6361</t>
+          <t>6579</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1658</t>
+          <t>1632</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12824</t>
+          <t>12823</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>29951</t>
+          <t>30904</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>40235</t>
+          <t>41194</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>75,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>20520</t>
+          <t>20302</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,34%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>54116</t>
+          <t>54368</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>65990</t>
+          <t>66094</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>79,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>97,09%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18047</t>
+          <t>18064</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>36846</t>
+          <t>36674</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>25721</t>
+          <t>27254</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>50848</t>
+          <t>51046</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>49142</t>
+          <t>48456</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>79749</t>
+          <t>77673</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,59%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>36290</t>
+          <t>35620</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>62253</t>
+          <t>61216</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>36409</t>
+          <t>35756</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>63520</t>
+          <t>62581</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>78855</t>
+          <t>78134</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>115365</t>
+          <t>114224</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,69%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>412889</t>
+          <t>413377</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>443230</t>
+          <t>443809</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>571453</t>
+          <t>572975</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>607620</t>
+          <t>608287</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>84,65%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>994367</t>
+          <t>994755</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1041130</t>
+          <t>1043104</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,45%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36802</t>
+          <t>36930</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>65622</t>
+          <t>64869</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>54736</t>
+          <t>55522</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>87043</t>
+          <t>88547</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>100038</t>
+          <t>101660</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>143386</t>
+          <t>143570</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,69%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>38766</t>
+          <t>39721</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>69957</t>
+          <t>68886</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>53158</t>
+          <t>52873</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>85027</t>
+          <t>84155</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>98460</t>
+          <t>97726</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>141487</t>
+          <t>141042</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,45%</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>289640</t>
+          <t>292668</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>329361</t>
+          <t>328250</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>69,89%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>79,48%</t>
+          <t>79,21%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>474261</t>
+          <t>475884</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>517068</t>
+          <t>517689</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>75,0%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>81,49%</t>
+          <t>81,58%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>778679</t>
+          <t>779671</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>833587</t>
+          <t>836975</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>74,23%</t>
+          <t>74,33%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>79,79%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1009</t>
+          <t>1062</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9927</t>
+          <t>11177</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8026</t>
+          <t>8438</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2354</t>
+          <t>2977</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>12960</t>
+          <t>13278</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,58%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6201</t>
+          <t>6175</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21566</t>
+          <t>20924</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2052</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11681</t>
+          <t>10667</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>10439</t>
+          <t>9295</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>27438</t>
+          <t>27808</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,78%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>91963</t>
+          <t>93593</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>109632</t>
+          <t>110086</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>68564</t>
+          <t>69000</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>79895</t>
+          <t>79896</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3520,7 +3520,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>167486</t>
+          <t>166563</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>186325</t>
+          <t>187191</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>82,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,79%</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3705,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4692</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5753</t>
+          <t>6829</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3775,7 +3775,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6606</t>
+          <t>6627</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,57%</t>
         </is>
       </c>
     </row>
@@ -3818,7 +3818,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5089</t>
+          <t>5334</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3833,7 +3833,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7114</t>
+          <t>6768</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3868,7 +3868,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>984</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8780</t>
+          <t>8978</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>18,39%</t>
         </is>
       </c>
     </row>
@@ -3926,7 +3926,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>19534</t>
+          <t>19941</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,51%</t>
+          <t>75,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13781</t>
+          <t>14101</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21242</t>
+          <t>21246</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>63,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>37117</t>
+          <t>37454</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>46756</t>
+          <t>46828</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,92%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>41497</t>
+          <t>41838</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>70429</t>
+          <t>71179</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>58957</t>
+          <t>58691</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>91726</t>
+          <t>93684</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>105848</t>
+          <t>108638</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>153107</t>
+          <t>153960</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,85%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>51034</t>
+          <t>49865</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>82120</t>
+          <t>84086</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>59142</t>
+          <t>59542</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>91274</t>
+          <t>91862</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>117676</t>
+          <t>118028</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>164039</t>
+          <t>164248</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,64%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>417477</t>
+          <t>417026</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>459168</t>
+          <t>459388</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>74,6%</t>
+          <t>74,52%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>82,09%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>569514</t>
+          <t>569196</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>611605</t>
+          <t>612355</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>76,93%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>82,77%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>999509</t>
+          <t>998477</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1059529</t>
+          <t>1063711</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>76,91%</t>
+          <t>76,84%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>81,86%</t>
         </is>
       </c>
     </row>
@@ -4843,12 +4843,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19749</t>
+          <t>20270</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37868</t>
+          <t>39915</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4858,49 +4858,49 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
+          <t>11,28%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>43920</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>31749</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>59352</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>7,92%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>5,72%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
           <t>10,7%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>43920</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>31498</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>60877</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>7,92%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>5,68%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>10,97%</t>
-        </is>
-      </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>67</t>
@@ -4913,12 +4913,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>56553</t>
+          <t>55532</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>90863</t>
+          <t>89937</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,9%</t>
         </is>
       </c>
     </row>
@@ -4956,12 +4956,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28190</t>
+          <t>27825</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>50764</t>
+          <t>50257</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>40246</t>
+          <t>39649</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>70599</t>
+          <t>70838</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>74491</t>
+          <t>73499</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>112545</t>
+          <t>112174</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,35%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>271975</t>
+          <t>272423</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>300921</t>
+          <t>300576</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>76,98%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>84,93%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>437572</t>
+          <t>434795</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>475627</t>
+          <t>476771</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>78,88%</t>
+          <t>78,38%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>85,94%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>720267</t>
+          <t>721197</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>768355</t>
+          <t>769456</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>79,27%</t>
+          <t>79,37%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>84,68%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2064</t>
+          <t>2228</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12644</t>
+          <t>12870</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1356</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>15544</t>
+          <t>16796</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5164</t>
+          <t>5266</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>21537</t>
+          <t>22190</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,83%</t>
         </is>
       </c>
     </row>
@@ -5412,12 +5412,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4032</t>
+          <t>4005</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14671</t>
+          <t>14581</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5427,12 +5427,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7554</t>
+          <t>7255</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>25882</t>
+          <t>24995</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>14587</t>
+          <t>14558</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>34545</t>
+          <t>34410</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,04%</t>
         </is>
       </c>
     </row>
@@ -5525,12 +5525,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>169704</t>
+          <t>170217</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>184195</t>
+          <t>184410</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>156269</t>
+          <t>156704</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>176723</t>
+          <t>176593</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>333291</t>
+          <t>331905</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>357033</t>
+          <t>357310</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,88%</t>
         </is>
       </c>
     </row>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4358</t>
+          <t>4453</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4428</t>
+          <t>3765</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5542</t>
+          <t>5153</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5908,7 +5908,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11657</t>
+          <t>10800</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5923,7 +5923,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1395</t>
+          <t>1593</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12494</t>
+          <t>13576</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>17,93%</t>
         </is>
       </c>
     </row>
@@ -5981,12 +5981,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>34522</t>
+          <t>35405</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>41306</t>
+          <t>41304</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5996,12 +5996,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>84,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>22017</t>
+          <t>22874</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>67,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>61799</t>
+          <t>61109</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>73913</t>
+          <t>73503</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6066,12 +6066,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>80,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,09%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>26176</t>
+          <t>25554</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>47445</t>
+          <t>46612</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>35967</t>
+          <t>35249</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>67114</t>
+          <t>67495</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>68487</t>
+          <t>68596</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>105172</t>
+          <t>107063</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,84%</t>
         </is>
       </c>
     </row>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>36147</t>
+          <t>37172</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>60935</t>
+          <t>61352</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6339,12 +6339,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>53733</t>
+          <t>54869</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>89692</t>
+          <t>90061</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6374,12 +6374,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>97526</t>
+          <t>98411</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>142808</t>
+          <t>139913</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,25%</t>
         </is>
       </c>
     </row>
@@ -6437,12 +6437,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>490286</t>
+          <t>489434</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>520941</t>
+          <t>519387</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>83,17%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,26%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>630354</t>
+          <t>632402</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>678442</t>
+          <t>677395</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6487,12 +6487,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>81,44%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1131310</t>
+          <t>1135050</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1187402</t>
+          <t>1186806</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>83,16%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>86,95%</t>
         </is>
       </c>
     </row>
@@ -6893,32 +6893,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>34162</t>
+          <t>35367</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26730</t>
+          <t>26995</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43447</t>
+          <t>45090</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6928,32 +6928,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>69051</t>
+          <t>73629</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>57884</t>
+          <t>61772</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>81776</t>
+          <t>85719</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6963,32 +6963,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>103212</t>
+          <t>108996</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>88851</t>
+          <t>95468</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>117511</t>
+          <t>122933</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>14,87%</t>
         </is>
       </c>
     </row>
@@ -7006,32 +7006,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>37708</t>
+          <t>39716</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29560</t>
+          <t>30293</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46841</t>
+          <t>49257</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7041,32 +7041,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>74590</t>
+          <t>80889</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>63729</t>
+          <t>69667</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>86050</t>
+          <t>93652</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7076,32 +7076,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>112299</t>
+          <t>120605</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>99665</t>
+          <t>105343</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>127225</t>
+          <t>135495</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,39%</t>
         </is>
       </c>
     </row>
@@ -7119,32 +7119,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>195195</t>
+          <t>212620</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>182125</t>
+          <t>200558</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>204529</t>
+          <t>224272</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>73,9%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>68,19%</t>
+          <t>69,71%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>77,95%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7154,32 +7154,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>357092</t>
+          <t>384263</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>342309</t>
+          <t>369741</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>371135</t>
+          <t>400231</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>71,31%</t>
+          <t>71,32%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>68,63%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>74,28%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7189,32 +7189,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>552287</t>
+          <t>596882</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>533636</t>
+          <t>576967</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>569796</t>
+          <t>615269</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>71,93%</t>
+          <t>72,22%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>69,5%</t>
+          <t>69,81%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>74,21%</t>
+          <t>74,44%</t>
         </is>
       </c>
     </row>
@@ -7232,17 +7232,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>267065</t>
+          <t>287703</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>267065</t>
+          <t>287703</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>267065</t>
+          <t>287703</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7267,17 +7267,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>500733</t>
+          <t>538781</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>500733</t>
+          <t>538781</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>500733</t>
+          <t>538781</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7302,17 +7302,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>767798</t>
+          <t>826483</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>767798</t>
+          <t>826483</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>767798</t>
+          <t>826483</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7349,22 +7349,22 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>12326</t>
+          <t>12912</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7714</t>
+          <t>8574</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18503</t>
+          <t>20286</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -7374,7 +7374,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7384,32 +7384,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>5948</t>
+          <t>6532</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1405</t>
+          <t>3816</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13223</t>
+          <t>11985</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7419,32 +7419,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>18273</t>
+          <t>19444</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>7619</t>
+          <t>13172</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>29086</t>
+          <t>27793</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -7462,22 +7462,22 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19130</t>
+          <t>20436</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12961</t>
+          <t>14409</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26951</t>
+          <t>29449</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -7487,7 +7487,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7497,32 +7497,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>23327</t>
+          <t>26758</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8042</t>
+          <t>20552</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>46339</t>
+          <t>34409</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7532,32 +7532,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>42457</t>
+          <t>47195</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>16721</t>
+          <t>38710</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>62748</t>
+          <t>58448</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>10,05%</t>
         </is>
       </c>
     </row>
@@ -7575,32 +7575,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>241802</t>
+          <t>270477</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>232510</t>
+          <t>259732</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>249622</t>
+          <t>277718</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7610,32 +7610,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>426464</t>
+          <t>244355</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>398924</t>
+          <t>235797</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>445571</t>
+          <t>251694</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>84,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7645,32 +7645,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>668266</t>
+          <t>514832</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>639950</t>
+          <t>503108</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>702965</t>
+          <t>526144</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>86,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>90,49%</t>
         </is>
       </c>
     </row>
@@ -7688,17 +7688,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>273257</t>
+          <t>303825</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>273257</t>
+          <t>303825</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>273257</t>
+          <t>303825</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7723,17 +7723,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>455739</t>
+          <t>277646</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>455739</t>
+          <t>277646</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>455739</t>
+          <t>277646</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7758,17 +7758,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>728996</t>
+          <t>581471</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>728996</t>
+          <t>581471</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>728996</t>
+          <t>581471</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7805,32 +7805,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1569</t>
+          <t>2137</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>544</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5172</t>
+          <t>6448</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7875,32 +7875,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1569</t>
+          <t>2137</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>551</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4574</t>
+          <t>6009</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -7918,32 +7918,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3383</t>
+          <t>4139</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11257</t>
+          <t>12732</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7953,32 +7953,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4787</t>
+          <t>5802</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2984</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8801</t>
+          <t>10386</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7988,32 +7988,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>11275</t>
+          <t>12884</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7044</t>
+          <t>8432</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16539</t>
+          <t>18977</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,41%</t>
         </is>
       </c>
     </row>
@@ -8031,32 +8031,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>96929</t>
+          <t>109662</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>91710</t>
+          <t>104293</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>100356</t>
+          <t>113669</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8066,32 +8066,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>66538</t>
+          <t>77053</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>62524</t>
+          <t>72469</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>69008</t>
+          <t>79871</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8101,32 +8101,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>163467</t>
+          <t>186715</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>158247</t>
+          <t>180429</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>168117</t>
+          <t>191751</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,05%</t>
         </is>
       </c>
     </row>
@@ -8144,17 +8144,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>104986</t>
+          <t>118881</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>104986</t>
+          <t>118881</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>104986</t>
+          <t>118881</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8179,17 +8179,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8214,17 +8214,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>176311</t>
+          <t>201736</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>176311</t>
+          <t>201736</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>176311</t>
+          <t>201736</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8261,32 +8261,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>48056</t>
+          <t>50416</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>39291</t>
+          <t>42057</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>59500</t>
+          <t>63273</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8296,32 +8296,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>74999</t>
+          <t>80162</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>36775</t>
+          <t>68633</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>97884</t>
+          <t>94198</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8331,32 +8331,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>123055</t>
+          <t>130577</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>82839</t>
+          <t>114340</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>149750</t>
+          <t>147896</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,19%</t>
         </is>
       </c>
     </row>
@@ -8374,32 +8374,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>63326</t>
+          <t>67234</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>52336</t>
+          <t>56285</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>77099</t>
+          <t>80687</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8409,32 +8409,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>102704</t>
+          <t>113449</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>47962</t>
+          <t>100004</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>132443</t>
+          <t>129724</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8444,32 +8444,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>166030</t>
+          <t>180683</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>97880</t>
+          <t>162180</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>195466</t>
+          <t>200510</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>12,46%</t>
         </is>
       </c>
     </row>
@@ -8487,32 +8487,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>533926</t>
+          <t>592759</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>518255</t>
+          <t>575449</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>547974</t>
+          <t>607036</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>81,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8522,32 +8522,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>850094</t>
+          <t>705671</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>799879</t>
+          <t>687487</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>943821</t>
+          <t>723565</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>78,47%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>77,82%</t>
+          <t>76,45%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>80,46%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8557,32 +8557,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1384019</t>
+          <t>1298430</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1334668</t>
+          <t>1273905</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1484238</t>
+          <t>1321945</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>80,66%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>79,14%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>82,12%</t>
         </is>
       </c>
     </row>
@@ -8600,17 +8600,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>645308</t>
+          <t>710409</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>645308</t>
+          <t>710409</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>645308</t>
+          <t>710409</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8635,17 +8635,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1027797</t>
+          <t>899282</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1027797</t>
+          <t>899282</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1027797</t>
+          <t>899282</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8670,17 +8670,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1673104</t>
+          <t>1609691</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1673104</t>
+          <t>1609691</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1673104</t>
+          <t>1609691</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
